--- a/diseases/d059/2015-2019.xlsx
+++ b/diseases/d059/2015-2019.xlsx
@@ -1061,9 +1061,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1457,9 +1454,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -2345,9 +2339,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
@@ -3233,9 +3224,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
@@ -4121,9 +4109,6 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
@@ -5157,9 +5142,6 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
@@ -6045,9 +6027,6 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
@@ -6933,9 +6912,6 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
@@ -7969,9 +7945,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -8857,9 +8830,6 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -9745,9 +9715,6 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
@@ -10781,9 +10748,6 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
@@ -11669,9 +11633,6 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
@@ -12705,9 +12666,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -13249,9 +13207,6 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
@@ -14137,9 +14092,6 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
@@ -15025,9 +14977,6 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
@@ -16061,9 +16010,6 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
@@ -16949,9 +16895,6 @@
       <c r="O110" t="n">
         <v>0</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0</v>
       </c>
@@ -17837,9 +17780,6 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0</v>
       </c>
@@ -18873,9 +18813,6 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0</v>
       </c>
@@ -19761,9 +19698,6 @@
       <c r="O129" t="n">
         <v>0</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0</v>
       </c>
@@ -20649,9 +20583,6 @@
       <c r="O135" t="n">
         <v>0</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0</v>
       </c>
@@ -21685,9 +21616,6 @@
       <c r="O142" t="n">
         <v>0</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0</v>
       </c>
@@ -22573,9 +22501,6 @@
       <c r="O148" t="n">
         <v>0</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0</v>
       </c>
@@ -23461,9 +23386,6 @@
       <c r="O154" t="n">
         <v>0</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0</v>
       </c>
@@ -24645,9 +24567,6 @@
       <c r="O162" t="n">
         <v>0</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0</v>
       </c>
@@ -25041,9 +24960,6 @@
       <c r="O164" t="n">
         <v>0</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0</v>
       </c>
@@ -25929,9 +25845,6 @@
       <c r="O170" t="n">
         <v>0</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0</v>
       </c>
@@ -26817,9 +26730,6 @@
       <c r="O176" t="n">
         <v>0</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0</v>
       </c>
@@ -27853,9 +27763,6 @@
       <c r="O183" t="n">
         <v>0</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>0</v>
       </c>
@@ -28741,9 +28648,6 @@
       <c r="O189" t="n">
         <v>0</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0</v>
       </c>
@@ -29629,9 +29533,6 @@
       <c r="O195" t="n">
         <v>0</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="R195" t="n">
         <v>0</v>
       </c>
@@ -30665,9 +30566,6 @@
       <c r="O202" t="n">
         <v>0</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="R202" t="n">
         <v>0</v>
       </c>
@@ -31553,9 +31451,6 @@
       <c r="O208" t="n">
         <v>0</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>0</v>
       </c>
@@ -32589,9 +32484,6 @@
       <c r="O215" t="n">
         <v>0</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="R215" t="n">
         <v>0</v>
       </c>
@@ -33477,9 +33369,6 @@
       <c r="O221" t="n">
         <v>0</v>
       </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
       <c r="R221" t="n">
         <v>0</v>
       </c>
@@ -34365,9 +34254,6 @@
       <c r="O227" t="n">
         <v>0</v>
       </c>
-      <c r="Q227" t="n">
-        <v>0</v>
-      </c>
       <c r="R227" t="n">
         <v>0</v>
       </c>
@@ -35401,9 +35287,6 @@
       <c r="O234" t="n">
         <v>0</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="R234" t="n">
         <v>0</v>
       </c>
@@ -36437,9 +36320,6 @@
       <c r="O241" t="n">
         <v>0</v>
       </c>
-      <c r="Q241" t="n">
-        <v>0</v>
-      </c>
       <c r="R241" t="n">
         <v>0</v>
       </c>
@@ -36833,9 +36713,6 @@
       <c r="O243" t="n">
         <v>0</v>
       </c>
-      <c r="Q243" t="n">
-        <v>0</v>
-      </c>
       <c r="R243" t="n">
         <v>0</v>
       </c>
@@ -37721,9 +37598,6 @@
       <c r="O249" t="n">
         <v>0</v>
       </c>
-      <c r="Q249" t="n">
-        <v>0</v>
-      </c>
       <c r="R249" t="n">
         <v>0</v>
       </c>
@@ -38609,9 +38483,6 @@
       <c r="O255" t="n">
         <v>0</v>
       </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
       <c r="R255" t="n">
         <v>0</v>
       </c>
@@ -39645,9 +39516,6 @@
       <c r="O262" t="n">
         <v>0</v>
       </c>
-      <c r="Q262" t="n">
-        <v>0</v>
-      </c>
       <c r="R262" t="n">
         <v>0</v>
       </c>
@@ -40533,9 +40401,6 @@
       <c r="O268" t="n">
         <v>0</v>
       </c>
-      <c r="Q268" t="n">
-        <v>0</v>
-      </c>
       <c r="R268" t="n">
         <v>0</v>
       </c>
@@ -41569,9 +41434,6 @@
       <c r="O275" t="n">
         <v>0</v>
       </c>
-      <c r="Q275" t="n">
-        <v>0</v>
-      </c>
       <c r="R275" t="n">
         <v>0</v>
       </c>
@@ -42457,9 +42319,6 @@
       <c r="O281" t="n">
         <v>0</v>
       </c>
-      <c r="Q281" t="n">
-        <v>0</v>
-      </c>
       <c r="R281" t="n">
         <v>0</v>
       </c>
@@ -43345,9 +43204,6 @@
       <c r="O287" t="n">
         <v>0</v>
       </c>
-      <c r="Q287" t="n">
-        <v>0</v>
-      </c>
       <c r="R287" t="n">
         <v>0</v>
       </c>
@@ -44381,9 +44237,6 @@
       <c r="O294" t="n">
         <v>0</v>
       </c>
-      <c r="Q294" t="n">
-        <v>0</v>
-      </c>
       <c r="R294" t="n">
         <v>0</v>
       </c>
@@ -45269,9 +45122,6 @@
       <c r="O300" t="n">
         <v>0</v>
       </c>
-      <c r="Q300" t="n">
-        <v>0</v>
-      </c>
       <c r="R300" t="n">
         <v>0</v>
       </c>
@@ -46157,9 +46007,6 @@
       <c r="O306" t="n">
         <v>0</v>
       </c>
-      <c r="Q306" t="n">
-        <v>0</v>
-      </c>
       <c r="R306" t="n">
         <v>0</v>
       </c>
@@ -47193,9 +47040,6 @@
       <c r="O313" t="n">
         <v>0</v>
       </c>
-      <c r="Q313" t="n">
-        <v>0</v>
-      </c>
       <c r="R313" t="n">
         <v>0</v>
       </c>
@@ -48229,9 +48073,6 @@
       <c r="O320" t="n">
         <v>0</v>
       </c>
-      <c r="Q320" t="n">
-        <v>0</v>
-      </c>
       <c r="R320" t="n">
         <v>0</v>
       </c>
@@ -48625,9 +48466,6 @@
       <c r="O322" t="n">
         <v>0</v>
       </c>
-      <c r="Q322" t="n">
-        <v>0</v>
-      </c>
       <c r="R322" t="n">
         <v>0</v>
       </c>
@@ -49661,9 +49499,6 @@
       <c r="O329" t="n">
         <v>0</v>
       </c>
-      <c r="Q329" t="n">
-        <v>0</v>
-      </c>
       <c r="R329" t="n">
         <v>0</v>
       </c>
@@ -50549,9 +50384,6 @@
       <c r="O335" t="n">
         <v>0</v>
       </c>
-      <c r="Q335" t="n">
-        <v>0</v>
-      </c>
       <c r="R335" t="n">
         <v>0</v>
       </c>
@@ -51437,9 +51269,6 @@
       <c r="O341" t="n">
         <v>0</v>
       </c>
-      <c r="Q341" t="n">
-        <v>0</v>
-      </c>
       <c r="R341" t="n">
         <v>0</v>
       </c>
@@ -52325,9 +52154,6 @@
       <c r="O347" t="n">
         <v>0</v>
       </c>
-      <c r="Q347" t="n">
-        <v>0</v>
-      </c>
       <c r="R347" t="n">
         <v>0</v>
       </c>
@@ -53361,9 +53187,6 @@
       <c r="O354" t="n">
         <v>0</v>
       </c>
-      <c r="Q354" t="n">
-        <v>0</v>
-      </c>
       <c r="R354" t="n">
         <v>0</v>
       </c>
@@ -54249,9 +54072,6 @@
       <c r="O360" t="n">
         <v>0</v>
       </c>
-      <c r="Q360" t="n">
-        <v>0</v>
-      </c>
       <c r="R360" t="n">
         <v>0</v>
       </c>
@@ -55137,9 +54957,6 @@
       <c r="O366" t="n">
         <v>0</v>
       </c>
-      <c r="Q366" t="n">
-        <v>0</v>
-      </c>
       <c r="R366" t="n">
         <v>0</v>
       </c>
@@ -56173,9 +55990,6 @@
       <c r="O373" t="n">
         <v>0</v>
       </c>
-      <c r="Q373" t="n">
-        <v>0</v>
-      </c>
       <c r="R373" t="n">
         <v>0</v>
       </c>
@@ -57061,9 +56875,6 @@
       <c r="O379" t="n">
         <v>0</v>
       </c>
-      <c r="Q379" t="n">
-        <v>0</v>
-      </c>
       <c r="R379" t="n">
         <v>0</v>
       </c>
@@ -58097,9 +57908,6 @@
       <c r="O386" t="n">
         <v>0</v>
       </c>
-      <c r="Q386" t="n">
-        <v>0</v>
-      </c>
       <c r="R386" t="n">
         <v>0</v>
       </c>
@@ -58983,9 +58791,6 @@
         <v>0</v>
       </c>
       <c r="O392" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q392" t="n">
         <v>0</v>
       </c>
       <c r="R392" t="n">
